--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WISCONSIN_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WISCONSIN_2022.xlsx
@@ -409,7 +409,7 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="4">
@@ -1471,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="63">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C94">
@@ -2281,7 +2281,7 @@
         <v>7</v>
       </c>
       <c r="D107">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="108">
@@ -2461,7 +2461,7 @@
         <v>73</v>
       </c>
       <c r="D117">
-        <v>0.009941440827999455</v>
+        <v>0.009941440827999456</v>
       </c>
     </row>
     <row r="118">
@@ -2731,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="D132">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="133">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C133">
@@ -4171,7 +4171,7 @@
         <v>7</v>
       </c>
       <c r="D212">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="213">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C224">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -4729,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="244">
@@ -5089,7 +5089,7 @@
         <v>7</v>
       </c>
       <c r="D263">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="264">
@@ -5755,7 +5755,7 @@
         <v>7</v>
       </c>
       <c r="D300">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="301">
@@ -6097,7 +6097,7 @@
         <v>7</v>
       </c>
       <c r="D319">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="320">
@@ -6745,7 +6745,7 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="356">
@@ -7195,7 +7195,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="381">
@@ -8635,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="D460">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="461">
@@ -9517,7 +9517,7 @@
         <v>7</v>
       </c>
       <c r="D509">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="510">
@@ -10237,7 +10237,7 @@
         <v>7</v>
       </c>
       <c r="D549">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="550">
@@ -10363,7 +10363,7 @@
         <v>7</v>
       </c>
       <c r="D556">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="557">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C606">
@@ -11569,7 +11569,7 @@
         <v>7</v>
       </c>
       <c r="D623">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="624">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C653">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C657">
@@ -13459,7 +13459,7 @@
         <v>7</v>
       </c>
       <c r="D728">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="729">
@@ -13855,7 +13855,7 @@
         <v>69</v>
       </c>
       <c r="D750">
-        <v>0.009396704344273457</v>
+        <v>0.009396704344273456</v>
       </c>
     </row>
     <row r="751">
@@ -14251,7 +14251,7 @@
         <v>7</v>
       </c>
       <c r="D772">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="773">
@@ -15115,7 +15115,7 @@
         <v>7</v>
       </c>
       <c r="D820">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="821">
@@ -16267,7 +16267,7 @@
         <v>7</v>
       </c>
       <c r="D884">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="885">
@@ -17149,7 +17149,7 @@
         <v>7</v>
       </c>
       <c r="D933">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="934">
@@ -18355,7 +18355,7 @@
         <v>7</v>
       </c>
       <c r="D1000">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="1001">
@@ -19129,7 +19129,7 @@
         <v>7</v>
       </c>
       <c r="D1043">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="1044">
@@ -20281,7 +20281,7 @@
         <v>69</v>
       </c>
       <c r="D1107">
-        <v>0.009396704344273457</v>
+        <v>0.009396704344273456</v>
       </c>
     </row>
     <row r="1108">
@@ -20515,7 +20515,7 @@
         <v>7</v>
       </c>
       <c r="D1120">
-        <v>0.0009532888465204957</v>
+        <v>0.0009532888465204956</v>
       </c>
     </row>
     <row r="1121">
